--- a/redmine-mantencion/assets/templates/plantilla-usuarios-nextcloud-v2.xlsx
+++ b/redmine-mantencion/assets/templates/plantilla-usuarios-nextcloud-v2.xlsx
@@ -7,9 +7,71 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>NOVA</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>Ingresar RUT sin puntos, sin guion y sin digito verificador. Si viene con DV, el sistema intentara normalizarlo.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>Ingresar nombre completo de la persona.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>Ingresar correo institucional o correo autorizado.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Calibri"/>
+          </rPr>
+          <t>Ingresar servicio, unidad o grupo. El sistema buscara la mejor coincidencia en Nextcloud.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -18,12 +80,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -41,7 +97,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -49,96 +105,67 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D7DE"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D7DE"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D7DE"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D7DE"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="36" customWidth="1"/>
+    <col min="1" max="1" width="18" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="36" customWidth="1"/>
+    <col min="4" max="4" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="22" customHeight="1">
       <c r="A1" t="inlineStr" s="1">
         <is>
-          <t>Nombre de usuario</t>
+          <t>RUT</t>
         </is>
       </c>
       <c r="B1" t="inlineStr" s="1">
         <is>
-          <t>Nombre a desplegar</t>
+          <t>Nombre</t>
         </is>
       </c>
       <c r="C1" t="inlineStr" s="1">
         <is>
-          <t>Correo electrónico</t>
+          <t>Correo</t>
         </is>
       </c>
       <c r="D1" t="inlineStr" s="1">
         <is>
-          <t>Grupo</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr" s="2">
-        <is>
-          <t>RUT con dígito verificador, sin puntos. Ej: 19006667</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr" s="2">
-        <is>
-          <t>Ej: Jean Cortes Lorca</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr" s="2">
-        <is>
-          <t>Correo institucional</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr" s="2">
-        <is>
-          <t>Grupo o servicio para buscar coincidencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>19006667</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Jean Cortes Lorca</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>jcortes@coresalud.cl</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Informática</t>
+          <t>Servicio</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:D1"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>